--- a/registros.xlsx
+++ b/registros.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G776"/>
+  <dimension ref="A1:G834"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1457,10 +1457,14 @@
           <t>17,09</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>R$ 17,09</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -1486,10 +1490,14 @@
           <t>78,74</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>R$ 78,74</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -1515,10 +1523,14 @@
           <t>32,01</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>R$ 32,01</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -1544,10 +1556,14 @@
           <t>147,44</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>R$ 147,44</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -1577,10 +1593,14 @@
           <t>7,83</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>R$ 7,83</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -1610,10 +1630,14 @@
           <t>36,09</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>R$ 36,09</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -1643,10 +1667,14 @@
           <t>16,9</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>R$ 16,90</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -1676,10 +1704,14 @@
           <t>77,84</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>R$ 77,84</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -1709,10 +1741,14 @@
           <t>665,97</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>R$ 665,97</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -1742,10 +1778,14 @@
           <t>3067,51</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>R$ 3.067,51</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -1775,10 +1815,14 @@
           <t>799,17</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>R$ 799,17</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -1808,10 +1852,14 @@
           <t>3681,01</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>R$ 3.681,01</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -1841,10 +1889,14 @@
           <t>1128,88</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>R$ 1.128,88</t>
+        </is>
+      </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -1874,10 +1926,14 @@
           <t>5199,7</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>R$ 5.199,70</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -1907,10 +1963,14 @@
           <t>1128,88</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>R$ 1.128,88</t>
+        </is>
+      </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -1940,10 +2000,14 @@
           <t>5199,7</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>R$ 5.199,70</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -1973,10 +2037,14 @@
           <t>1173</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>R$ 1.173,00</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -2006,10 +2074,14 @@
           <t>5402,92</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>R$ 5.402,92</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -2039,10 +2111,14 @@
           <t>616,71</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>R$ 616,71</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -2072,10 +2148,14 @@
           <t>2840,58</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>R$ 2.840,58</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -2105,10 +2185,14 @@
           <t>4,23</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>R$ 4,23</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -2138,10 +2222,14 @@
           <t>19,47</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>R$ 19,47</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -2171,10 +2259,14 @@
           <t>7,04</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>R$ 7,04</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -2204,10 +2296,14 @@
           <t>32,44</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>R$ 32,44</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -2237,10 +2333,14 @@
           <t>12,83</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>R$ 12,83</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -2270,10 +2370,14 @@
           <t>59,1</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>R$ 59,10</t>
+        </is>
+      </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -2303,10 +2407,14 @@
           <t>1143,21</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>R$ 1.143,21</t>
+        </is>
+      </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -2336,10 +2444,14 @@
           <t>5265,71</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>R$ 5.265,71</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -2369,10 +2481,14 @@
           <t>85,53</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>R$ 85,53</t>
+        </is>
+      </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -2402,10 +2518,14 @@
           <t>393,96</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>R$ 393,96</t>
+        </is>
+      </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -2435,10 +2555,14 @@
           <t>15,49</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>R$ 15,49</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -2468,10 +2592,14 @@
           <t>71,35</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>R$ 71,35</t>
+        </is>
+      </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -2501,10 +2629,14 @@
           <t>22,69</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>R$ 22,69</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -2534,10 +2666,14 @@
           <t>104,49</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>R$ 104,49</t>
+        </is>
+      </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -2567,10 +2703,14 @@
           <t>10,95</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>R$ 10,95</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -2600,10 +2740,14 @@
           <t>50,42</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>R$ 50,42</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -2633,10 +2777,14 @@
           <t>5,12</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>R$ 5,12</t>
+        </is>
+      </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -2666,10 +2814,14 @@
           <t>23,57</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>R$ 23,57</t>
+        </is>
+      </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -2699,10 +2851,14 @@
           <t>2,59</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>R$ 2,59</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -2732,10 +2888,14 @@
           <t>11,92</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>R$ 11,92</t>
+        </is>
+      </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -2765,10 +2925,14 @@
           <t>1831,67</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>R$ 1.831,67</t>
+        </is>
+      </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -2798,10 +2962,14 @@
           <t>8436,8</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>R$ 8.436,80</t>
+        </is>
+      </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -2831,10 +2999,14 @@
           <t>154,34</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>R$ 154,34</t>
+        </is>
+      </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -2864,10 +3036,14 @@
           <t>710,87</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>R$ 710,87</t>
+        </is>
+      </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -2897,10 +3073,14 @@
           <t>185,11</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>R$ 185,11</t>
+        </is>
+      </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -2930,10 +3110,14 @@
           <t>852,65</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>R$ 852,65</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -2963,10 +3147,14 @@
           <t>107,17</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>R$ 107,17</t>
+        </is>
+      </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -2996,10 +3184,14 @@
           <t>493,63</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>R$ 493,63</t>
+        </is>
+      </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -3029,10 +3221,14 @@
           <t>1597,98</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>R$ 1.597,98</t>
+        </is>
+      </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -3062,10 +3258,14 @@
           <t>7360,36</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>R$ 7.360,36</t>
+        </is>
+      </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -3095,10 +3295,14 @@
           <t>2,72</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>R$ 2,72</t>
+        </is>
+      </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -3128,10 +3332,14 @@
           <t>12,51</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>R$ 12,51</t>
+        </is>
+      </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -3161,10 +3369,14 @@
           <t>16156,1</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>R$ 16.156,10</t>
+        </is>
+      </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -3194,10 +3406,14 @@
           <t>74415,96</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>R$ 74.415,96</t>
+        </is>
+      </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -3227,10 +3443,14 @@
           <t>753,07</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>R$ 753,07</t>
+        </is>
+      </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -3260,10 +3480,14 @@
           <t>3468,69</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>R$ 3.468,69</t>
+        </is>
+      </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -3293,10 +3517,14 @@
           <t>8,1</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>R$ 8,10</t>
+        </is>
+      </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -3326,10 +3554,14 @@
           <t>37,29</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>R$ 37,29</t>
+        </is>
+      </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -3359,10 +3591,14 @@
           <t>35,29</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>R$ 3,53</t>
+        </is>
+      </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>complemento</t>
         </is>
       </c>
     </row>
@@ -3392,10 +3628,14 @@
           <t>162,51</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>R$ 146,33</t>
+        </is>
+      </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>complemento</t>
         </is>
       </c>
     </row>
@@ -11565,10 +11805,14 @@
           <t>5,72</t>
         </is>
       </c>
-      <c r="F312" t="inlineStr"/>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>R$ 5,72</t>
+        </is>
+      </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -11598,10 +11842,14 @@
           <t>26,3</t>
         </is>
       </c>
-      <c r="F313" t="inlineStr"/>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>R$ 26,30</t>
+        </is>
+      </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -11631,10 +11879,14 @@
           <t>204,76</t>
         </is>
       </c>
-      <c r="F314" t="inlineStr"/>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>R$ 204,76</t>
+        </is>
+      </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -11664,10 +11916,14 @@
           <t>943,15</t>
         </is>
       </c>
-      <c r="F315" t="inlineStr"/>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>R$ 943,15</t>
+        </is>
+      </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -11697,10 +11953,14 @@
           <t>67,75</t>
         </is>
       </c>
-      <c r="F316" t="inlineStr"/>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>R$ 67,75</t>
+        </is>
+      </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -11730,10 +11990,14 @@
           <t>312,05</t>
         </is>
       </c>
-      <c r="F317" t="inlineStr"/>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>R$ 312,05</t>
+        </is>
+      </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -11763,10 +12027,14 @@
           <t>42,33</t>
         </is>
       </c>
-      <c r="F318" t="inlineStr"/>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>R$ 42,33</t>
+        </is>
+      </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -11796,10 +12064,14 @@
           <t>194,97</t>
         </is>
       </c>
-      <c r="F319" t="inlineStr"/>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>R$ 194,97</t>
+        </is>
+      </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -11829,10 +12101,14 @@
           <t>665,34</t>
         </is>
       </c>
-      <c r="F320" t="inlineStr"/>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>R$ 665,34</t>
+        </is>
+      </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -11862,10 +12138,14 @@
           <t>3064,68</t>
         </is>
       </c>
-      <c r="F321" t="inlineStr"/>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>R$ 3.064,68</t>
+        </is>
+      </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -14855,10 +15135,14 @@
           <t>35,91</t>
         </is>
       </c>
-      <c r="F402" t="inlineStr"/>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>R$ 35,91</t>
+        </is>
+      </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -14888,10 +15172,14 @@
           <t>165,39</t>
         </is>
       </c>
-      <c r="F403" t="inlineStr"/>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>R$ 165,39</t>
+        </is>
+      </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -14921,10 +15209,14 @@
           <t>912,16</t>
         </is>
       </c>
-      <c r="F404" t="inlineStr"/>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>R$ 912,16</t>
+        </is>
+      </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -14954,10 +15246,14 @@
           <t>4201,56</t>
         </is>
       </c>
-      <c r="F405" t="inlineStr"/>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>R$ 4.201,56</t>
+        </is>
+      </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -19205,10 +19501,14 @@
           <t>196,89</t>
         </is>
       </c>
-      <c r="F520" t="inlineStr"/>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>R$ 196,89</t>
+        </is>
+      </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -19238,10 +19538,14 @@
           <t>906,92</t>
         </is>
       </c>
-      <c r="F521" t="inlineStr"/>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>R$ 906,92</t>
+        </is>
+      </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -19271,10 +19575,14 @@
           <t>5545,41</t>
         </is>
       </c>
-      <c r="F522" t="inlineStr"/>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>R$ 5.545,41</t>
+        </is>
+      </c>
       <c r="G522" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -19304,10 +19612,14 @@
           <t>25542,5</t>
         </is>
       </c>
-      <c r="F523" t="inlineStr"/>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>R$ 25.542,50</t>
+        </is>
+      </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -19337,10 +19649,14 @@
           <t>1,75</t>
         </is>
       </c>
-      <c r="F524" t="inlineStr"/>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>R$ 1,75</t>
+        </is>
+      </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -19370,10 +19686,14 @@
           <t>8,08</t>
         </is>
       </c>
-      <c r="F525" t="inlineStr"/>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>R$ 8,08</t>
+        </is>
+      </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -20589,12 +20909,12 @@
       </c>
       <c r="F558" t="inlineStr">
         <is>
-          <t>R$ 66,80</t>
+          <t>R$ 32,01</t>
         </is>
       </c>
       <c r="G558" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>complemento</t>
         </is>
       </c>
     </row>
@@ -20626,12 +20946,12 @@
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>R$ 307,68</t>
+          <t>R$ 147,44</t>
         </is>
       </c>
       <c r="G559" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>complemento</t>
         </is>
       </c>
     </row>
@@ -21027,10 +21347,14 @@
           <t>3,19</t>
         </is>
       </c>
-      <c r="F570" t="inlineStr"/>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>R$ 3,19</t>
+        </is>
+      </c>
       <c r="G570" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -21056,10 +21380,14 @@
           <t>73,27</t>
         </is>
       </c>
-      <c r="F571" t="inlineStr"/>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>R$ 73,27</t>
+        </is>
+      </c>
       <c r="G571" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -21085,10 +21413,14 @@
           <t>6,27</t>
         </is>
       </c>
-      <c r="F572" t="inlineStr"/>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>R$ 6,27</t>
+        </is>
+      </c>
       <c r="G572" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -21114,10 +21446,14 @@
           <t>1,56</t>
         </is>
       </c>
-      <c r="F573" t="inlineStr"/>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>R$ 1,95</t>
+        </is>
+      </c>
       <c r="G573" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>estorno</t>
         </is>
       </c>
     </row>
@@ -21143,10 +21479,14 @@
           <t>5,22</t>
         </is>
       </c>
-      <c r="F574" t="inlineStr"/>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>R$ 5,22</t>
+        </is>
+      </c>
       <c r="G574" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -21172,10 +21512,14 @@
           <t>1,1</t>
         </is>
       </c>
-      <c r="F575" t="inlineStr"/>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>R$ 1,10</t>
+        </is>
+      </c>
       <c r="G575" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -21201,10 +21545,14 @@
           <t>4,71</t>
         </is>
       </c>
-      <c r="F576" t="inlineStr"/>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>R$ 4,71</t>
+        </is>
+      </c>
       <c r="G576" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -21230,10 +21578,14 @@
           <t>14,69</t>
         </is>
       </c>
-      <c r="F577" t="inlineStr"/>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>R$ 14,69</t>
+        </is>
+      </c>
       <c r="G577" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -21259,10 +21611,14 @@
           <t>337,48</t>
         </is>
       </c>
-      <c r="F578" t="inlineStr"/>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>R$ 337,48</t>
+        </is>
+      </c>
       <c r="G578" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -21288,10 +21644,14 @@
           <t>28,9</t>
         </is>
       </c>
-      <c r="F579" t="inlineStr"/>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>R$ 28,90</t>
+        </is>
+      </c>
       <c r="G579" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -21317,10 +21677,14 @@
           <t>7,19</t>
         </is>
       </c>
-      <c r="F580" t="inlineStr"/>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>R$ 9,00</t>
+        </is>
+      </c>
       <c r="G580" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>estorno</t>
         </is>
       </c>
     </row>
@@ -21346,10 +21710,14 @@
           <t>24,05</t>
         </is>
       </c>
-      <c r="F581" t="inlineStr"/>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>R$ 24,05</t>
+        </is>
+      </c>
       <c r="G581" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -21375,10 +21743,14 @@
           <t>5,06</t>
         </is>
       </c>
-      <c r="F582" t="inlineStr"/>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>R$ 5,06</t>
+        </is>
+      </c>
       <c r="G582" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -21404,10 +21776,14 @@
           <t>21,69</t>
         </is>
       </c>
-      <c r="F583" t="inlineStr"/>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>R$ 21,69</t>
+        </is>
+      </c>
       <c r="G583" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -21437,10 +21813,14 @@
           <t>156,52</t>
         </is>
       </c>
-      <c r="F584" t="inlineStr"/>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>R$ 156,52</t>
+        </is>
+      </c>
       <c r="G584" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -21470,10 +21850,14 @@
           <t>3,3</t>
         </is>
       </c>
-      <c r="F585" t="inlineStr"/>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>R$ 3,30</t>
+        </is>
+      </c>
       <c r="G585" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -21503,10 +21887,14 @@
           <t>136,95</t>
         </is>
       </c>
-      <c r="F586" t="inlineStr"/>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>R$ 136,95</t>
+        </is>
+      </c>
       <c r="G586" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -21536,10 +21924,14 @@
           <t>7,67</t>
         </is>
       </c>
-      <c r="F587" t="inlineStr"/>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>R$ 7,67</t>
+        </is>
+      </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -21569,10 +21961,14 @@
           <t>3,07</t>
         </is>
       </c>
-      <c r="F588" t="inlineStr"/>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>R$ 3,07</t>
+        </is>
+      </c>
       <c r="G588" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -21602,10 +21998,14 @@
           <t>7,26</t>
         </is>
       </c>
-      <c r="F589" t="inlineStr"/>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>R$ 7,26</t>
+        </is>
+      </c>
       <c r="G589" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -21635,10 +22035,14 @@
           <t>8,25</t>
         </is>
       </c>
-      <c r="F590" t="inlineStr"/>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>R$ 8,25</t>
+        </is>
+      </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -21668,10 +22072,14 @@
           <t>83,63</t>
         </is>
       </c>
-      <c r="F591" t="inlineStr"/>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>R$ 83,63</t>
+        </is>
+      </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -21701,10 +22109,14 @@
           <t>43,14</t>
         </is>
       </c>
-      <c r="F592" t="inlineStr"/>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>R$ 43,14</t>
+        </is>
+      </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -21734,10 +22146,14 @@
           <t>4,13</t>
         </is>
       </c>
-      <c r="F593" t="inlineStr"/>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>R$ 4,13</t>
+        </is>
+      </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -21767,10 +22183,14 @@
           <t>85,25</t>
         </is>
       </c>
-      <c r="F594" t="inlineStr"/>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>R$ 85,25</t>
+        </is>
+      </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -21800,10 +22220,14 @@
           <t>12,08</t>
         </is>
       </c>
-      <c r="F595" t="inlineStr"/>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>R$ 12,08</t>
+        </is>
+      </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -21833,10 +22257,14 @@
           <t>3,28</t>
         </is>
       </c>
-      <c r="F596" t="inlineStr"/>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>R$ 3,28</t>
+        </is>
+      </c>
       <c r="G596" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -21866,10 +22294,14 @@
           <t>100,19</t>
         </is>
       </c>
-      <c r="F597" t="inlineStr"/>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>R$ 100,19</t>
+        </is>
+      </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -21899,10 +22331,14 @@
           <t>79,67</t>
         </is>
       </c>
-      <c r="F598" t="inlineStr"/>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>R$ 79,67</t>
+        </is>
+      </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -21932,10 +22368,14 @@
           <t>24,01</t>
         </is>
       </c>
-      <c r="F599" t="inlineStr"/>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>R$ 24,01</t>
+        </is>
+      </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -21965,10 +22405,14 @@
           <t>72,12</t>
         </is>
       </c>
-      <c r="F600" t="inlineStr"/>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>R$ 72,12</t>
+        </is>
+      </c>
       <c r="G600" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -21998,10 +22442,14 @@
           <t>14,35</t>
         </is>
       </c>
-      <c r="F601" t="inlineStr"/>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>R$ 14,35</t>
+        </is>
+      </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -22031,10 +22479,14 @@
           <t>3,92</t>
         </is>
       </c>
-      <c r="F602" t="inlineStr"/>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>R$ 3,92</t>
+        </is>
+      </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -22064,10 +22516,14 @@
           <t>3,8</t>
         </is>
       </c>
-      <c r="F603" t="inlineStr"/>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>R$ 3,80</t>
+        </is>
+      </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -22097,10 +22553,14 @@
           <t>3,02</t>
         </is>
       </c>
-      <c r="F604" t="inlineStr"/>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>R$ 3,02</t>
+        </is>
+      </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -22130,10 +22590,14 @@
           <t>2,48</t>
         </is>
       </c>
-      <c r="F605" t="inlineStr"/>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>R$ 2,48</t>
+        </is>
+      </c>
       <c r="G605" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -22163,10 +22627,14 @@
           <t>5,84</t>
         </is>
       </c>
-      <c r="F606" t="inlineStr"/>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>R$ 5,84</t>
+        </is>
+      </c>
       <c r="G606" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -22196,10 +22664,14 @@
           <t>4,07</t>
         </is>
       </c>
-      <c r="F607" t="inlineStr"/>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>R$ 4,07</t>
+        </is>
+      </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -22229,10 +22701,14 @@
           <t>1,99</t>
         </is>
       </c>
-      <c r="F608" t="inlineStr"/>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>R$ 1,99</t>
+        </is>
+      </c>
       <c r="G608" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -22262,10 +22738,14 @@
           <t>15,35</t>
         </is>
       </c>
-      <c r="F609" t="inlineStr"/>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>R$ 15,35</t>
+        </is>
+      </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -22295,10 +22775,14 @@
           <t>3,15</t>
         </is>
       </c>
-      <c r="F610" t="inlineStr"/>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>R$ 3,15</t>
+        </is>
+      </c>
       <c r="G610" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -22328,10 +22812,14 @@
           <t>6,6</t>
         </is>
       </c>
-      <c r="F611" t="inlineStr"/>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>R$ 6,60</t>
+        </is>
+      </c>
       <c r="G611" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -22361,10 +22849,14 @@
           <t>720,94</t>
         </is>
       </c>
-      <c r="F612" t="inlineStr"/>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>R$ 720,94</t>
+        </is>
+      </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -22394,10 +22886,14 @@
           <t>15,19</t>
         </is>
       </c>
-      <c r="F613" t="inlineStr"/>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>R$ 15,19</t>
+        </is>
+      </c>
       <c r="G613" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -22427,10 +22923,14 @@
           <t>630,8</t>
         </is>
       </c>
-      <c r="F614" t="inlineStr"/>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>R$ 630,80</t>
+        </is>
+      </c>
       <c r="G614" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -22460,10 +22960,14 @@
           <t>35,34</t>
         </is>
       </c>
-      <c r="F615" t="inlineStr"/>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>R$ 35,34</t>
+        </is>
+      </c>
       <c r="G615" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -22493,10 +22997,14 @@
           <t>14,14</t>
         </is>
       </c>
-      <c r="F616" t="inlineStr"/>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>R$ 14,13</t>
+        </is>
+      </c>
       <c r="G616" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>complemento</t>
         </is>
       </c>
     </row>
@@ -22526,10 +23034,14 @@
           <t>33,46</t>
         </is>
       </c>
-      <c r="F617" t="inlineStr"/>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>R$ 33,46</t>
+        </is>
+      </c>
       <c r="G617" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -22559,10 +23071,14 @@
           <t>38</t>
         </is>
       </c>
-      <c r="F618" t="inlineStr"/>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>R$ 38,00</t>
+        </is>
+      </c>
       <c r="G618" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -22592,10 +23108,14 @@
           <t>385,21</t>
         </is>
       </c>
-      <c r="F619" t="inlineStr"/>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>R$ 385,21</t>
+        </is>
+      </c>
       <c r="G619" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -22625,10 +23145,14 @@
           <t>198,72</t>
         </is>
       </c>
-      <c r="F620" t="inlineStr"/>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>R$ 198,72</t>
+        </is>
+      </c>
       <c r="G620" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -22658,10 +23182,14 @@
           <t>19</t>
         </is>
       </c>
-      <c r="F621" t="inlineStr"/>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>R$ 19,00</t>
+        </is>
+      </c>
       <c r="G621" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -22691,10 +23219,14 @@
           <t>392,67</t>
         </is>
       </c>
-      <c r="F622" t="inlineStr"/>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>R$ 392,67</t>
+        </is>
+      </c>
       <c r="G622" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -22724,10 +23256,14 @@
           <t>55,62</t>
         </is>
       </c>
-      <c r="F623" t="inlineStr"/>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>R$ 55,62</t>
+        </is>
+      </c>
       <c r="G623" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -22757,10 +23293,14 @@
           <t>15,11</t>
         </is>
       </c>
-      <c r="F624" t="inlineStr"/>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>R$ 15,11</t>
+        </is>
+      </c>
       <c r="G624" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -22790,10 +23330,14 @@
           <t>461,47</t>
         </is>
       </c>
-      <c r="F625" t="inlineStr"/>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>R$ 461,47</t>
+        </is>
+      </c>
       <c r="G625" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -22823,10 +23367,14 @@
           <t>366,96</t>
         </is>
       </c>
-      <c r="F626" t="inlineStr"/>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>R$ 366,96</t>
+        </is>
+      </c>
       <c r="G626" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -22856,10 +23404,14 @@
           <t>110,61</t>
         </is>
       </c>
-      <c r="F627" t="inlineStr"/>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>R$ 110,61</t>
+        </is>
+      </c>
       <c r="G627" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -22889,10 +23441,14 @@
           <t>332,2</t>
         </is>
       </c>
-      <c r="F628" t="inlineStr"/>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>R$ 332,20</t>
+        </is>
+      </c>
       <c r="G628" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -22922,10 +23478,14 @@
           <t>66,08</t>
         </is>
       </c>
-      <c r="F629" t="inlineStr"/>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>R$ 66,08</t>
+        </is>
+      </c>
       <c r="G629" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -22955,10 +23515,14 @@
           <t>18,6</t>
         </is>
       </c>
-      <c r="F630" t="inlineStr"/>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>R$ 18,06</t>
+        </is>
+      </c>
       <c r="G630" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>complemento</t>
         </is>
       </c>
     </row>
@@ -22988,10 +23552,14 @@
           <t>17,51</t>
         </is>
       </c>
-      <c r="F631" t="inlineStr"/>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>R$ 17,51</t>
+        </is>
+      </c>
       <c r="G631" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -23021,10 +23589,14 @@
           <t>13,91</t>
         </is>
       </c>
-      <c r="F632" t="inlineStr"/>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>R$ 13,91</t>
+        </is>
+      </c>
       <c r="G632" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -23054,10 +23626,14 @@
           <t>11,4</t>
         </is>
       </c>
-      <c r="F633" t="inlineStr"/>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>R$ 11,40</t>
+        </is>
+      </c>
       <c r="G633" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -23087,10 +23663,14 @@
           <t>26,88</t>
         </is>
       </c>
-      <c r="F634" t="inlineStr"/>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>R$ 26,88</t>
+        </is>
+      </c>
       <c r="G634" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -23120,10 +23700,14 @@
           <t>18,73</t>
         </is>
       </c>
-      <c r="F635" t="inlineStr"/>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>R$ 18,73</t>
+        </is>
+      </c>
       <c r="G635" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -23153,10 +23737,14 @@
           <t>9,19</t>
         </is>
       </c>
-      <c r="F636" t="inlineStr"/>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>R$ 9,19</t>
+        </is>
+      </c>
       <c r="G636" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -23186,10 +23774,14 @@
           <t>70,68</t>
         </is>
       </c>
-      <c r="F637" t="inlineStr"/>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>R$ 70,68</t>
+        </is>
+      </c>
       <c r="G637" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -23219,10 +23811,14 @@
           <t>14,51</t>
         </is>
       </c>
-      <c r="F638" t="inlineStr"/>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>R$ 14,51</t>
+        </is>
+      </c>
       <c r="G638" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -23252,10 +23848,14 @@
           <t>30,4</t>
         </is>
       </c>
-      <c r="F639" t="inlineStr"/>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>R$ 30,40</t>
+        </is>
+      </c>
       <c r="G639" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -24671,10 +25271,14 @@
           <t>1,1</t>
         </is>
       </c>
-      <c r="F682" t="inlineStr"/>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>R$ 1,10</t>
+        </is>
+      </c>
       <c r="G682" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>ok</t>
         </is>
       </c>
     </row>
@@ -26627,13 +27231,13 @@
       </c>
       <c r="D742" t="inlineStr">
         <is>
-          <t>COFINS</t>
+          <t>PIS</t>
         </is>
       </c>
       <c r="E742" t="inlineStr"/>
       <c r="F742" t="inlineStr">
         <is>
-          <t>R$ 12.375,73</t>
+          <t>R$ 1,42</t>
         </is>
       </c>
       <c r="G742" t="inlineStr">
@@ -26660,13 +27264,13 @@
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>PIS</t>
+          <t>COFINS</t>
         </is>
       </c>
       <c r="E743" t="inlineStr"/>
       <c r="F743" t="inlineStr">
         <is>
-          <t>R$ 2.686,84</t>
+          <t>R$ 1.305,33</t>
         </is>
       </c>
       <c r="G743" t="inlineStr">
@@ -26699,7 +27303,7 @@
       <c r="E744" t="inlineStr"/>
       <c r="F744" t="inlineStr">
         <is>
-          <t>R$ 263.419,02</t>
+          <t>R$ 1.995,57</t>
         </is>
       </c>
       <c r="G744" t="inlineStr">
@@ -26732,7 +27336,7 @@
       <c r="E745" t="inlineStr"/>
       <c r="F745" t="inlineStr">
         <is>
-          <t>R$ 57.148,26</t>
+          <t>R$ 10,50</t>
         </is>
       </c>
       <c r="G745" t="inlineStr">
@@ -26754,18 +27358,18 @@
       </c>
       <c r="C746" t="inlineStr">
         <is>
-          <t>04.784.935/0011-39</t>
+          <t>04.784.935/0001-67</t>
         </is>
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>COFINS</t>
+          <t>PIS</t>
         </is>
       </c>
       <c r="E746" t="inlineStr"/>
       <c r="F746" t="inlineStr">
         <is>
-          <t>R$ 11,99</t>
+          <t>R$ 101,90</t>
         </is>
       </c>
       <c r="G746" t="inlineStr">
@@ -26787,18 +27391,18 @@
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>04.784.935/0011-39</t>
+          <t>04.784.935/0001-67</t>
         </is>
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t>PIS</t>
+          <t>COFINS</t>
         </is>
       </c>
       <c r="E747" t="inlineStr"/>
       <c r="F747" t="inlineStr">
         <is>
-          <t>R$ 2,60</t>
+          <t>R$ 12.375,73</t>
         </is>
       </c>
       <c r="G747" t="inlineStr">
@@ -26820,18 +27424,18 @@
       </c>
       <c r="C748" t="inlineStr">
         <is>
-          <t>04.784.935/0012-10</t>
+          <t>04.784.935/0001-67</t>
         </is>
       </c>
       <c r="D748" t="inlineStr">
         <is>
-          <t>PIS</t>
+          <t>COFINS</t>
         </is>
       </c>
       <c r="E748" t="inlineStr"/>
       <c r="F748" t="inlineStr">
         <is>
-          <t>R$ 1,17</t>
+          <t>R$ 15.475,30</t>
         </is>
       </c>
       <c r="G748" t="inlineStr">
@@ -26853,7 +27457,7 @@
       </c>
       <c r="C749" t="inlineStr">
         <is>
-          <t>04.784.935/0012-10</t>
+          <t>04.784.935/0001-67</t>
         </is>
       </c>
       <c r="D749" t="inlineStr">
@@ -26864,7 +27468,7 @@
       <c r="E749" t="inlineStr"/>
       <c r="F749" t="inlineStr">
         <is>
-          <t>R$ 5,37</t>
+          <t>R$ 16,01</t>
         </is>
       </c>
       <c r="G749" t="inlineStr">
@@ -26881,23 +27485,23 @@
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="C750" t="inlineStr">
         <is>
-          <t>3974</t>
+          <t>04.784.935/0001-67</t>
         </is>
       </c>
       <c r="D750" t="inlineStr">
         <is>
-          <t>COFINS</t>
+          <t>PIS</t>
         </is>
       </c>
       <c r="E750" t="inlineStr"/>
       <c r="F750" t="inlineStr">
         <is>
-          <t>R$ 190,87</t>
+          <t>R$ 169,87</t>
         </is>
       </c>
       <c r="G750" t="inlineStr">
@@ -26914,12 +27518,12 @@
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
         <is>
-          <t>3974</t>
+          <t>04.784.935/0001-67</t>
         </is>
       </c>
       <c r="D751" t="inlineStr">
@@ -26930,7 +27534,7 @@
       <c r="E751" t="inlineStr"/>
       <c r="F751" t="inlineStr">
         <is>
-          <t>R$ 190,87</t>
+          <t>R$ 2.376,87</t>
         </is>
       </c>
       <c r="G751" t="inlineStr">
@@ -26947,12 +27551,12 @@
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
         <is>
-          <t>3974</t>
+          <t>04.784.935/0001-67</t>
         </is>
       </c>
       <c r="D752" t="inlineStr">
@@ -26963,7 +27567,7 @@
       <c r="E752" t="inlineStr"/>
       <c r="F752" t="inlineStr">
         <is>
-          <t>R$ 41,43</t>
+          <t>R$ 2.686,84</t>
         </is>
       </c>
       <c r="G752" t="inlineStr">
@@ -26980,23 +27584,23 @@
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>3974</t>
+          <t>04.784.935/0001-67</t>
         </is>
       </c>
       <c r="D753" t="inlineStr">
         <is>
-          <t>PIS</t>
+          <t>COFINS</t>
         </is>
       </c>
       <c r="E753" t="inlineStr"/>
       <c r="F753" t="inlineStr">
         <is>
-          <t>R$ 41,43</t>
+          <t>R$ 26.696,21</t>
         </is>
       </c>
       <c r="G753" t="inlineStr">
@@ -27013,12 +27617,12 @@
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
         <is>
-          <t>3975</t>
+          <t>04.784.935/0001-67</t>
         </is>
       </c>
       <c r="D754" t="inlineStr">
@@ -27029,7 +27633,7 @@
       <c r="E754" t="inlineStr"/>
       <c r="F754" t="inlineStr">
         <is>
-          <t>R$ 190,87</t>
+          <t>R$ 263.419,02</t>
         </is>
       </c>
       <c r="G754" t="inlineStr">
@@ -27046,23 +27650,23 @@
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
         <is>
-          <t>3975</t>
+          <t>04.784.935/0001-67</t>
         </is>
       </c>
       <c r="D755" t="inlineStr">
         <is>
-          <t>COFINS</t>
+          <t>PIS</t>
         </is>
       </c>
       <c r="E755" t="inlineStr"/>
       <c r="F755" t="inlineStr">
         <is>
-          <t>R$ 190,87</t>
+          <t>R$ 283,39</t>
         </is>
       </c>
       <c r="G755" t="inlineStr">
@@ -27079,12 +27683,12 @@
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>3975</t>
+          <t>04.784.935/0001-67</t>
         </is>
       </c>
       <c r="D756" t="inlineStr">
@@ -27095,7 +27699,7 @@
       <c r="E756" t="inlineStr"/>
       <c r="F756" t="inlineStr">
         <is>
-          <t>R$ 41,43</t>
+          <t>R$ 3,48</t>
         </is>
       </c>
       <c r="G756" t="inlineStr">
@@ -27112,12 +27716,12 @@
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
         <is>
-          <t>3975</t>
+          <t>04.784.935/0001-67</t>
         </is>
       </c>
       <c r="D757" t="inlineStr">
@@ -27128,7 +27732,7 @@
       <c r="E757" t="inlineStr"/>
       <c r="F757" t="inlineStr">
         <is>
-          <t>R$ 41,43</t>
+          <t>R$ 3.359,77</t>
         </is>
       </c>
       <c r="G757" t="inlineStr">
@@ -27148,16 +27752,20 @@
           <t>LC</t>
         </is>
       </c>
-      <c r="C758" t="inlineStr"/>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>04.784.935/0001-67</t>
+        </is>
+      </c>
       <c r="D758" t="inlineStr">
         <is>
-          <t>PIS</t>
+          <t>COFINS</t>
         </is>
       </c>
       <c r="E758" t="inlineStr"/>
       <c r="F758" t="inlineStr">
         <is>
-          <t>R$ 0,01</t>
+          <t>R$ 34.130,93</t>
         </is>
       </c>
       <c r="G758" t="inlineStr">
@@ -27177,7 +27785,11 @@
           <t>LC</t>
         </is>
       </c>
-      <c r="C759" t="inlineStr"/>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>04.784.935/0001-67</t>
+        </is>
+      </c>
       <c r="D759" t="inlineStr">
         <is>
           <t>PIS</t>
@@ -27186,7 +27798,7 @@
       <c r="E759" t="inlineStr"/>
       <c r="F759" t="inlineStr">
         <is>
-          <t>R$ 0,02</t>
+          <t>R$ 433,25</t>
         </is>
       </c>
       <c r="G759" t="inlineStr">
@@ -27206,7 +27818,11 @@
           <t>LC</t>
         </is>
       </c>
-      <c r="C760" t="inlineStr"/>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>04.784.935/0001-67</t>
+        </is>
+      </c>
       <c r="D760" t="inlineStr">
         <is>
           <t>COFINS</t>
@@ -27215,7 +27831,7 @@
       <c r="E760" t="inlineStr"/>
       <c r="F760" t="inlineStr">
         <is>
-          <t>R$ 0,02</t>
+          <t>R$ 469,35</t>
         </is>
       </c>
       <c r="G760" t="inlineStr">
@@ -27235,7 +27851,11 @@
           <t>LC</t>
         </is>
       </c>
-      <c r="C761" t="inlineStr"/>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>04.784.935/0001-67</t>
+        </is>
+      </c>
       <c r="D761" t="inlineStr">
         <is>
           <t>COFINS</t>
@@ -27244,7 +27864,7 @@
       <c r="E761" t="inlineStr"/>
       <c r="F761" t="inlineStr">
         <is>
-          <t>R$ 0,02</t>
+          <t>R$ 48,41</t>
         </is>
       </c>
       <c r="G761" t="inlineStr">
@@ -27264,16 +27884,20 @@
           <t>LC</t>
         </is>
       </c>
-      <c r="C762" t="inlineStr"/>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>04.784.935/0001-67</t>
+        </is>
+      </c>
       <c r="D762" t="inlineStr">
         <is>
-          <t>COFINS</t>
+          <t>PIS</t>
         </is>
       </c>
       <c r="E762" t="inlineStr"/>
       <c r="F762" t="inlineStr">
         <is>
-          <t>R$ 0,02</t>
+          <t>R$ 5.795,89</t>
         </is>
       </c>
       <c r="G762" t="inlineStr">
@@ -27293,16 +27917,20 @@
           <t>LC</t>
         </is>
       </c>
-      <c r="C763" t="inlineStr"/>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>04.784.935/0001-67</t>
+        </is>
+      </c>
       <c r="D763" t="inlineStr">
         <is>
-          <t>COFINS</t>
+          <t>PIS</t>
         </is>
       </c>
       <c r="E763" t="inlineStr"/>
       <c r="F763" t="inlineStr">
         <is>
-          <t>R$ 0,02</t>
+          <t>R$ 516,03</t>
         </is>
       </c>
       <c r="G763" t="inlineStr">
@@ -27322,16 +27950,20 @@
           <t>LC</t>
         </is>
       </c>
-      <c r="C764" t="inlineStr"/>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>04.784.935/0001-67</t>
+        </is>
+      </c>
       <c r="D764" t="inlineStr">
         <is>
-          <t>COFINS</t>
+          <t>PIS</t>
         </is>
       </c>
       <c r="E764" t="inlineStr"/>
       <c r="F764" t="inlineStr">
         <is>
-          <t>R$ 0,02</t>
+          <t>R$ 57.148,26</t>
         </is>
       </c>
       <c r="G764" t="inlineStr">
@@ -27351,7 +27983,11 @@
           <t>LC</t>
         </is>
       </c>
-      <c r="C765" t="inlineStr"/>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>04.784.935/0001-67</t>
+        </is>
+      </c>
       <c r="D765" t="inlineStr">
         <is>
           <t>COFINS</t>
@@ -27360,7 +27996,7 @@
       <c r="E765" t="inlineStr"/>
       <c r="F765" t="inlineStr">
         <is>
-          <t>R$ 0,02</t>
+          <t>R$ 6,55</t>
         </is>
       </c>
       <c r="G765" t="inlineStr">
@@ -27380,16 +28016,20 @@
           <t>LC</t>
         </is>
       </c>
-      <c r="C766" t="inlineStr"/>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>04.784.935/0001-67</t>
+        </is>
+      </c>
       <c r="D766" t="inlineStr">
         <is>
-          <t>COFINS</t>
+          <t>PIS</t>
         </is>
       </c>
       <c r="E766" t="inlineStr"/>
       <c r="F766" t="inlineStr">
         <is>
-          <t>R$ 0,02</t>
+          <t>R$ 7.410,03</t>
         </is>
       </c>
       <c r="G766" t="inlineStr">
@@ -27409,7 +28049,11 @@
           <t>LC</t>
         </is>
       </c>
-      <c r="C767" t="inlineStr"/>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>04.784.935/0001-67</t>
+        </is>
+      </c>
       <c r="D767" t="inlineStr">
         <is>
           <t>COFINS</t>
@@ -27418,7 +28062,7 @@
       <c r="E767" t="inlineStr"/>
       <c r="F767" t="inlineStr">
         <is>
-          <t>R$ 0,02</t>
+          <t>R$ 782,45</t>
         </is>
       </c>
       <c r="G767" t="inlineStr">
@@ -27438,7 +28082,11 @@
           <t>LC</t>
         </is>
       </c>
-      <c r="C768" t="inlineStr"/>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>04.784.935/0005-90</t>
+        </is>
+      </c>
       <c r="D768" t="inlineStr">
         <is>
           <t>PIS</t>
@@ -27447,7 +28095,7 @@
       <c r="E768" t="inlineStr"/>
       <c r="F768" t="inlineStr">
         <is>
-          <t>R$ 0,03</t>
+          <t>R$ 113,80</t>
         </is>
       </c>
       <c r="G768" t="inlineStr">
@@ -27467,16 +28115,20 @@
           <t>LC</t>
         </is>
       </c>
-      <c r="C769" t="inlineStr"/>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>04.784.935/0005-90</t>
+        </is>
+      </c>
       <c r="D769" t="inlineStr">
         <is>
-          <t>PIS</t>
+          <t>COFINS</t>
         </is>
       </c>
       <c r="E769" t="inlineStr"/>
       <c r="F769" t="inlineStr">
         <is>
-          <t>R$ 0,04</t>
+          <t>R$ 17,23</t>
         </is>
       </c>
       <c r="G769" t="inlineStr">
@@ -27496,16 +28148,20 @@
           <t>LC</t>
         </is>
       </c>
-      <c r="C770" t="inlineStr"/>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>04.784.935/0005-90</t>
+        </is>
+      </c>
       <c r="D770" t="inlineStr">
         <is>
-          <t>COFINS</t>
+          <t>PIS</t>
         </is>
       </c>
       <c r="E770" t="inlineStr"/>
       <c r="F770" t="inlineStr">
         <is>
-          <t>R$ 0,05</t>
+          <t>R$ 3,74</t>
         </is>
       </c>
       <c r="G770" t="inlineStr">
@@ -27525,16 +28181,20 @@
           <t>LC</t>
         </is>
       </c>
-      <c r="C771" t="inlineStr"/>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>04.784.935/0005-90</t>
+        </is>
+      </c>
       <c r="D771" t="inlineStr">
         <is>
-          <t>PIS</t>
+          <t>COFINS</t>
         </is>
       </c>
       <c r="E771" t="inlineStr"/>
       <c r="F771" t="inlineStr">
         <is>
-          <t>R$ 123,17</t>
+          <t>R$ 524,27</t>
         </is>
       </c>
       <c r="G771" t="inlineStr">
@@ -27554,16 +28214,20 @@
           <t>LC</t>
         </is>
       </c>
-      <c r="C772" t="inlineStr"/>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>04.784.935/0008-33</t>
+        </is>
+      </c>
       <c r="D772" t="inlineStr">
         <is>
-          <t>COFINS</t>
+          <t>PIS</t>
         </is>
       </c>
       <c r="E772" t="inlineStr"/>
       <c r="F772" t="inlineStr">
         <is>
-          <t>R$ 20.365,76</t>
+          <t>R$ 0,76</t>
         </is>
       </c>
       <c r="G772" t="inlineStr">
@@ -27583,16 +28247,20 @@
           <t>LC</t>
         </is>
       </c>
-      <c r="C773" t="inlineStr"/>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>04.784.935/0008-33</t>
+        </is>
+      </c>
       <c r="D773" t="inlineStr">
         <is>
-          <t>COFINS</t>
+          <t>PIS</t>
         </is>
       </c>
       <c r="E773" t="inlineStr"/>
       <c r="F773" t="inlineStr">
         <is>
-          <t>R$ 3.223,75</t>
+          <t>R$ 1,83</t>
         </is>
       </c>
       <c r="G773" t="inlineStr">
@@ -27612,7 +28280,11 @@
           <t>LC</t>
         </is>
       </c>
-      <c r="C774" t="inlineStr"/>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>04.784.935/0008-33</t>
+        </is>
+      </c>
       <c r="D774" t="inlineStr">
         <is>
           <t>PIS</t>
@@ -27621,7 +28293,7 @@
       <c r="E774" t="inlineStr"/>
       <c r="F774" t="inlineStr">
         <is>
-          <t>R$ 4.412,58</t>
+          <t>R$ 118,35</t>
         </is>
       </c>
       <c r="G774" t="inlineStr">
@@ -27641,7 +28313,11 @@
           <t>LC</t>
         </is>
       </c>
-      <c r="C775" t="inlineStr"/>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>04.784.935/0008-33</t>
+        </is>
+      </c>
       <c r="D775" t="inlineStr">
         <is>
           <t>PIS</t>
@@ -27650,7 +28326,7 @@
       <c r="E775" t="inlineStr"/>
       <c r="F775" t="inlineStr">
         <is>
-          <t>R$ 700,33</t>
+          <t>R$ 18,87</t>
         </is>
       </c>
       <c r="G775" t="inlineStr">
@@ -27670,7 +28346,11 @@
           <t>LC</t>
         </is>
       </c>
-      <c r="C776" t="inlineStr"/>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>04.784.935/0008-33</t>
+        </is>
+      </c>
       <c r="D776" t="inlineStr">
         <is>
           <t>COFINS</t>
@@ -27679,10 +28359,1848 @@
       <c r="E776" t="inlineStr"/>
       <c r="F776" t="inlineStr">
         <is>
+          <t>R$ 3,49</t>
+        </is>
+      </c>
+      <c r="G776" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>04.784.935/0008-33</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>COFINS</t>
+        </is>
+      </c>
+      <c r="E777" t="inlineStr"/>
+      <c r="F777" t="inlineStr">
+        <is>
+          <t>R$ 545,14</t>
+        </is>
+      </c>
+      <c r="G777" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>04.784.935/0008-33</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>COFINS</t>
+        </is>
+      </c>
+      <c r="E778" t="inlineStr"/>
+      <c r="F778" t="inlineStr">
+        <is>
+          <t>R$ 8,37</t>
+        </is>
+      </c>
+      <c r="G778" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>04.784.935/0008-33</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>COFINS</t>
+        </is>
+      </c>
+      <c r="E779" t="inlineStr"/>
+      <c r="F779" t="inlineStr">
+        <is>
+          <t>R$ 86,94</t>
+        </is>
+      </c>
+      <c r="G779" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>04.784.935/0009-14</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>COFINS</t>
+        </is>
+      </c>
+      <c r="E780" t="inlineStr"/>
+      <c r="F780" t="inlineStr">
+        <is>
+          <t>R$ 133,75</t>
+        </is>
+      </c>
+      <c r="G780" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>04.784.935/0009-14</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>COFINS</t>
+        </is>
+      </c>
+      <c r="E781" t="inlineStr"/>
+      <c r="F781" t="inlineStr">
+        <is>
+          <t>R$ 133,75</t>
+        </is>
+      </c>
+      <c r="G781" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>04.784.935/0009-14</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>PIS</t>
+        </is>
+      </c>
+      <c r="E782" t="inlineStr"/>
+      <c r="F782" t="inlineStr">
+        <is>
+          <t>R$ 29,04</t>
+        </is>
+      </c>
+      <c r="G782" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>04.784.935/0009-14</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>PIS</t>
+        </is>
+      </c>
+      <c r="E783" t="inlineStr"/>
+      <c r="F783" t="inlineStr">
+        <is>
+          <t>R$ 29,04</t>
+        </is>
+      </c>
+      <c r="G783" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>04.784.935/0011-39</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>COFINS</t>
+        </is>
+      </c>
+      <c r="E784" t="inlineStr"/>
+      <c r="F784" t="inlineStr">
+        <is>
+          <t>R$ 1.265,83</t>
+        </is>
+      </c>
+      <c r="G784" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>04.784.935/0011-39</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>COFINS</t>
+        </is>
+      </c>
+      <c r="E785" t="inlineStr"/>
+      <c r="F785" t="inlineStr">
+        <is>
+          <t>R$ 11,99</t>
+        </is>
+      </c>
+      <c r="G785" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>04.784.935/0011-39</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>COFINS</t>
+        </is>
+      </c>
+      <c r="E786" t="inlineStr"/>
+      <c r="F786" t="inlineStr">
+        <is>
+          <t>R$ 17,70</t>
+        </is>
+      </c>
+      <c r="G786" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>04.784.935/0011-39</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>PIS</t>
+        </is>
+      </c>
+      <c r="E787" t="inlineStr"/>
+      <c r="F787" t="inlineStr">
+        <is>
+          <t>R$ 2,60</t>
+        </is>
+      </c>
+      <c r="G787" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>04.784.935/0011-39</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>PIS</t>
+        </is>
+      </c>
+      <c r="E788" t="inlineStr"/>
+      <c r="F788" t="inlineStr">
+        <is>
+          <t>R$ 274,82</t>
+        </is>
+      </c>
+      <c r="G788" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>04.784.935/0011-39</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>PIS</t>
+        </is>
+      </c>
+      <c r="E789" t="inlineStr"/>
+      <c r="F789" t="inlineStr">
+        <is>
+          <t>R$ 3,84</t>
+        </is>
+      </c>
+      <c r="G789" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>04.784.935/0012-10</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>PIS</t>
+        </is>
+      </c>
+      <c r="E790" t="inlineStr"/>
+      <c r="F790" t="inlineStr">
+        <is>
+          <t>R$ 1,17</t>
+        </is>
+      </c>
+      <c r="G790" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>04.784.935/0012-10</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>PIS</t>
+        </is>
+      </c>
+      <c r="E791" t="inlineStr"/>
+      <c r="F791" t="inlineStr">
+        <is>
+          <t>R$ 1.020,35</t>
+        </is>
+      </c>
+      <c r="G791" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>04.784.935/0012-10</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>COFINS</t>
+        </is>
+      </c>
+      <c r="E792" t="inlineStr"/>
+      <c r="F792" t="inlineStr">
+        <is>
+          <t>R$ 19,09</t>
+        </is>
+      </c>
+      <c r="G792" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>04.784.935/0012-10</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>PIS</t>
+        </is>
+      </c>
+      <c r="E793" t="inlineStr"/>
+      <c r="F793" t="inlineStr">
+        <is>
+          <t>R$ 2,05</t>
+        </is>
+      </c>
+      <c r="G793" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>04.784.935/0012-10</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>COFINS</t>
+        </is>
+      </c>
+      <c r="E794" t="inlineStr"/>
+      <c r="F794" t="inlineStr">
+        <is>
+          <t>R$ 202,76</t>
+        </is>
+      </c>
+      <c r="G794" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>04.784.935/0012-10</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>PIS</t>
+        </is>
+      </c>
+      <c r="E795" t="inlineStr"/>
+      <c r="F795" t="inlineStr">
+        <is>
+          <t>R$ 214,00</t>
+        </is>
+      </c>
+      <c r="G795" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>04.784.935/0012-10</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>COFINS</t>
+        </is>
+      </c>
+      <c r="E796" t="inlineStr"/>
+      <c r="F796" t="inlineStr">
+        <is>
+          <t>R$ 3.197,91</t>
+        </is>
+      </c>
+      <c r="G796" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>04.784.935/0012-10</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>PIS</t>
+        </is>
+      </c>
+      <c r="E797" t="inlineStr"/>
+      <c r="F797" t="inlineStr">
+        <is>
+          <t>R$ 4,14</t>
+        </is>
+      </c>
+      <c r="G797" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>04.784.935/0012-10</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>COFINS</t>
+        </is>
+      </c>
+      <c r="E798" t="inlineStr"/>
+      <c r="F798" t="inlineStr">
+        <is>
+          <t>R$ 4.699,81</t>
+        </is>
+      </c>
+      <c r="G798" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>04.784.935/0012-10</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>PIS</t>
+        </is>
+      </c>
+      <c r="E799" t="inlineStr"/>
+      <c r="F799" t="inlineStr">
+        <is>
+          <t>R$ 44,02</t>
+        </is>
+      </c>
+      <c r="G799" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>04.784.935/0012-10</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>COFINS</t>
+        </is>
+      </c>
+      <c r="E800" t="inlineStr"/>
+      <c r="F800" t="inlineStr">
+        <is>
+          <t>R$ 5,37</t>
+        </is>
+      </c>
+      <c r="G800" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>04.784.935/0012-10</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>PIS</t>
+        </is>
+      </c>
+      <c r="E801" t="inlineStr"/>
+      <c r="F801" t="inlineStr">
+        <is>
+          <t>R$ 694,27</t>
+        </is>
+      </c>
+      <c r="G801" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>04.784.935/0012-10</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>COFINS</t>
+        </is>
+      </c>
+      <c r="E802" t="inlineStr"/>
+      <c r="F802" t="inlineStr">
+        <is>
+          <t>R$ 9,46</t>
+        </is>
+      </c>
+      <c r="G802" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>04.784.935/0012-10</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>COFINS</t>
+        </is>
+      </c>
+      <c r="E803" t="inlineStr"/>
+      <c r="F803" t="inlineStr">
+        <is>
+          <t>R$ 985,72</t>
+        </is>
+      </c>
+      <c r="G803" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>COFINS</t>
+        </is>
+      </c>
+      <c r="E804" t="inlineStr"/>
+      <c r="F804" t="inlineStr">
+        <is>
+          <t>R$ 18.825,85</t>
+        </is>
+      </c>
+      <c r="G804" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>COFINS</t>
+        </is>
+      </c>
+      <c r="E805" t="inlineStr"/>
+      <c r="F805" t="inlineStr">
+        <is>
+          <t>R$ 18.825,85</t>
+        </is>
+      </c>
+      <c r="G805" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>PIS</t>
+        </is>
+      </c>
+      <c r="E806" t="inlineStr"/>
+      <c r="F806" t="inlineStr">
+        <is>
+          <t>R$ 4.087,19</t>
+        </is>
+      </c>
+      <c r="G806" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>PIS</t>
+        </is>
+      </c>
+      <c r="E807" t="inlineStr"/>
+      <c r="F807" t="inlineStr">
+        <is>
+          <t>R$ 4.087,19</t>
+        </is>
+      </c>
+      <c r="G807" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>3974</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>COFINS</t>
+        </is>
+      </c>
+      <c r="E808" t="inlineStr"/>
+      <c r="F808" t="inlineStr">
+        <is>
+          <t>R$ 190,87</t>
+        </is>
+      </c>
+      <c r="G808" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>3974</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>COFINS</t>
+        </is>
+      </c>
+      <c r="E809" t="inlineStr"/>
+      <c r="F809" t="inlineStr">
+        <is>
+          <t>R$ 190,87</t>
+        </is>
+      </c>
+      <c r="G809" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>3974</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>PIS</t>
+        </is>
+      </c>
+      <c r="E810" t="inlineStr"/>
+      <c r="F810" t="inlineStr">
+        <is>
+          <t>R$ 41,43</t>
+        </is>
+      </c>
+      <c r="G810" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>3974</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>PIS</t>
+        </is>
+      </c>
+      <c r="E811" t="inlineStr"/>
+      <c r="F811" t="inlineStr">
+        <is>
+          <t>R$ 41,43</t>
+        </is>
+      </c>
+      <c r="G811" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>3975</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>COFINS</t>
+        </is>
+      </c>
+      <c r="E812" t="inlineStr"/>
+      <c r="F812" t="inlineStr">
+        <is>
+          <t>R$ 190,87</t>
+        </is>
+      </c>
+      <c r="G812" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>3975</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>COFINS</t>
+        </is>
+      </c>
+      <c r="E813" t="inlineStr"/>
+      <c r="F813" t="inlineStr">
+        <is>
+          <t>R$ 190,87</t>
+        </is>
+      </c>
+      <c r="G813" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>3975</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>PIS</t>
+        </is>
+      </c>
+      <c r="E814" t="inlineStr"/>
+      <c r="F814" t="inlineStr">
+        <is>
+          <t>R$ 41,43</t>
+        </is>
+      </c>
+      <c r="G814" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>3975</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>PIS</t>
+        </is>
+      </c>
+      <c r="E815" t="inlineStr"/>
+      <c r="F815" t="inlineStr">
+        <is>
+          <t>R$ 41,43</t>
+        </is>
+      </c>
+      <c r="G815" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr"/>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>PIS</t>
+        </is>
+      </c>
+      <c r="E816" t="inlineStr"/>
+      <c r="F816" t="inlineStr">
+        <is>
+          <t>R$ 0,01</t>
+        </is>
+      </c>
+      <c r="G816" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr"/>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>PIS</t>
+        </is>
+      </c>
+      <c r="E817" t="inlineStr"/>
+      <c r="F817" t="inlineStr">
+        <is>
+          <t>R$ 0,02</t>
+        </is>
+      </c>
+      <c r="G817" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr"/>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>COFINS</t>
+        </is>
+      </c>
+      <c r="E818" t="inlineStr"/>
+      <c r="F818" t="inlineStr">
+        <is>
+          <t>R$ 0,02</t>
+        </is>
+      </c>
+      <c r="G818" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr"/>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>COFINS</t>
+        </is>
+      </c>
+      <c r="E819" t="inlineStr"/>
+      <c r="F819" t="inlineStr">
+        <is>
+          <t>R$ 0,02</t>
+        </is>
+      </c>
+      <c r="G819" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr"/>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>COFINS</t>
+        </is>
+      </c>
+      <c r="E820" t="inlineStr"/>
+      <c r="F820" t="inlineStr">
+        <is>
+          <t>R$ 0,02</t>
+        </is>
+      </c>
+      <c r="G820" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr"/>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>COFINS</t>
+        </is>
+      </c>
+      <c r="E821" t="inlineStr"/>
+      <c r="F821" t="inlineStr">
+        <is>
+          <t>R$ 0,02</t>
+        </is>
+      </c>
+      <c r="G821" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr"/>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>COFINS</t>
+        </is>
+      </c>
+      <c r="E822" t="inlineStr"/>
+      <c r="F822" t="inlineStr">
+        <is>
+          <t>R$ 0,02</t>
+        </is>
+      </c>
+      <c r="G822" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr"/>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>COFINS</t>
+        </is>
+      </c>
+      <c r="E823" t="inlineStr"/>
+      <c r="F823" t="inlineStr">
+        <is>
+          <t>R$ 0,02</t>
+        </is>
+      </c>
+      <c r="G823" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr"/>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>COFINS</t>
+        </is>
+      </c>
+      <c r="E824" t="inlineStr"/>
+      <c r="F824" t="inlineStr">
+        <is>
+          <t>R$ 0,02</t>
+        </is>
+      </c>
+      <c r="G824" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr"/>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>COFINS</t>
+        </is>
+      </c>
+      <c r="E825" t="inlineStr"/>
+      <c r="F825" t="inlineStr">
+        <is>
+          <t>R$ 0,02</t>
+        </is>
+      </c>
+      <c r="G825" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr"/>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>PIS</t>
+        </is>
+      </c>
+      <c r="E826" t="inlineStr"/>
+      <c r="F826" t="inlineStr">
+        <is>
+          <t>R$ 0,03</t>
+        </is>
+      </c>
+      <c r="G826" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr"/>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>PIS</t>
+        </is>
+      </c>
+      <c r="E827" t="inlineStr"/>
+      <c r="F827" t="inlineStr">
+        <is>
+          <t>R$ 0,04</t>
+        </is>
+      </c>
+      <c r="G827" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr"/>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>COFINS</t>
+        </is>
+      </c>
+      <c r="E828" t="inlineStr"/>
+      <c r="F828" t="inlineStr">
+        <is>
+          <t>R$ 0,05</t>
+        </is>
+      </c>
+      <c r="G828" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr"/>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>PIS</t>
+        </is>
+      </c>
+      <c r="E829" t="inlineStr"/>
+      <c r="F829" t="inlineStr">
+        <is>
+          <t>R$ 123,17</t>
+        </is>
+      </c>
+      <c r="G829" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr"/>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>COFINS</t>
+        </is>
+      </c>
+      <c r="E830" t="inlineStr"/>
+      <c r="F830" t="inlineStr">
+        <is>
+          <t>R$ 20.365,76</t>
+        </is>
+      </c>
+      <c r="G830" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr"/>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>COFINS</t>
+        </is>
+      </c>
+      <c r="E831" t="inlineStr"/>
+      <c r="F831" t="inlineStr">
+        <is>
+          <t>R$ 3.223,75</t>
+        </is>
+      </c>
+      <c r="G831" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr"/>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>PIS</t>
+        </is>
+      </c>
+      <c r="E832" t="inlineStr"/>
+      <c r="F832" t="inlineStr">
+        <is>
+          <t>R$ 4.412,58</t>
+        </is>
+      </c>
+      <c r="G832" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr"/>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>PIS</t>
+        </is>
+      </c>
+      <c r="E833" t="inlineStr"/>
+      <c r="F833" t="inlineStr">
+        <is>
+          <t>R$ 700,33</t>
+        </is>
+      </c>
+      <c r="G833" t="inlineStr">
+        <is>
+          <t>so_sap</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr"/>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>COFINS</t>
+        </is>
+      </c>
+      <c r="E834" t="inlineStr"/>
+      <c r="F834" t="inlineStr">
+        <is>
           <t>R$ 757,99</t>
         </is>
       </c>
-      <c r="G776" t="inlineStr">
+      <c r="G834" t="inlineStr">
         <is>
           <t>so_sap</t>
         </is>

--- a/registros.xlsx
+++ b/registros.xlsx
@@ -873,12 +873,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>R$ 49,50</t>
+          <t>R$ 4.463,89</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>estorno</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>R$ 228,00</t>
+          <t>R$ 20.560,97</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>estorno</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>R$ 57,37</t>
+          <t>R$ 19,50</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>complemento</t>
         </is>
       </c>
     </row>
@@ -972,12 +972,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>R$ 264,27</t>
+          <t>R$ 90,00</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>complemento</t>
         </is>
       </c>
     </row>
@@ -1003,10 +1003,14 @@
           <t>808,5</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>R$ 19,50</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>complemento</t>
         </is>
       </c>
     </row>
@@ -1032,10 +1036,14 @@
           <t>3724</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>R$ 90,00</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>so_sped</t>
+          <t>complemento</t>
         </is>
       </c>
     </row>
@@ -1063,12 +1071,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>R$ 11,29</t>
+          <t>R$ 311,36</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>estorno</t>
         </is>
       </c>
     </row>
@@ -1096,12 +1104,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>R$ 52,02</t>
+          <t>R$ 1.434,16</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>estorno</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1137,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>R$ 20.008,30</t>
+          <t>R$ 1.285,16</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>complemento</t>
         </is>
       </c>
     </row>
@@ -1162,12 +1170,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>R$ 92.159,43</t>
+          <t>R$ 5.919,53</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>complemento</t>
         </is>
       </c>
     </row>
@@ -1195,12 +1203,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>R$ 49,50</t>
+          <t>R$ 882,69</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>estorno</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1236,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>R$ 228,00</t>
+          <t>R$ 4.065,72</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>estorno</t>
         </is>
       </c>
     </row>
@@ -1261,12 +1269,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>R$ 1.018,88</t>
+          <t>R$ 4.680,00</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>estorno</t>
         </is>
       </c>
     </row>
@@ -1294,12 +1302,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>R$ 4.693,00</t>
+          <t>R$ 21.600,00</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>estorno</t>
         </is>
       </c>
     </row>
@@ -1327,12 +1335,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>R$ 7.084,90</t>
+          <t>R$ 5.205,83</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>complemento</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1368,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>R$ 32.633,46</t>
+          <t>R$ 23.978,39</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>complemento</t>
         </is>
       </c>
     </row>
@@ -1393,12 +1401,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>R$ 1,22</t>
+          <t>R$ 49,50</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>estorno</t>
         </is>
       </c>
     </row>
@@ -1426,12 +1434,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>R$ 5,61</t>
+          <t>R$ 228,00</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>estorno</t>
         </is>
       </c>
     </row>
